--- a/data/trans_bre/P16-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 21,24</t>
+          <t>11,34; 21,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,92</t>
+          <t>11,51; 21,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 22,53</t>
+          <t>11,96; 22,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 14,09</t>
+          <t>4,22; 14,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 55,41</t>
+          <t>26,49; 56,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,44; 44,45</t>
+          <t>20,66; 43,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 48,23</t>
+          <t>22,53; 47,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 27,46</t>
+          <t>6,83; 28,72</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,3</t>
+          <t>13,23; 22,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,62; 25,16</t>
+          <t>16,56; 25,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 20,73</t>
+          <t>12,24; 20,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 43,63</t>
+          <t>14,83; 43,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,99; 57,46</t>
+          <t>30,47; 57,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 52,86</t>
+          <t>31,56; 52,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,62; 44,54</t>
+          <t>23,98; 44,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,27; 207,79</t>
+          <t>31,13; 211,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 24,87</t>
+          <t>13,62; 24,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 25,15</t>
+          <t>14,81; 25,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 19,56</t>
+          <t>9,93; 19,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 29,5</t>
+          <t>1,58; 32,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,09; 69,92</t>
+          <t>32,8; 67,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,92; 56,39</t>
+          <t>29,52; 56,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 44,55</t>
+          <t>20,42; 45,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 56,97</t>
+          <t>2,85; 63,23</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 22,76</t>
+          <t>14,15; 23,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 25,01</t>
+          <t>16,26; 25,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 16,96</t>
+          <t>7,52; 16,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 19,4</t>
+          <t>7,23; 19,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,29; 59,79</t>
+          <t>33,48; 61,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 51,11</t>
+          <t>30,03; 51,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 33,97</t>
+          <t>13,5; 32,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 34,78</t>
+          <t>11,99; 34,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,7; 20,48</t>
+          <t>15,68; 20,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,37</t>
+          <t>17,36; 22,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,55</t>
+          <t>12,82; 17,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 29,75</t>
+          <t>11,03; 29,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,43; 52,27</t>
+          <t>37,4; 52,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,9; 45,53</t>
+          <t>33,5; 45,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,97; 36,07</t>
+          <t>25,34; 35,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,34; 75,12</t>
+          <t>20,5; 75,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>8,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 21,45</t>
+          <t>11,31; 21,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 21,63</t>
+          <t>11,13; 21,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 22,61</t>
+          <t>11,93; 22,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,77</t>
+          <t>3,49; 13,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,49; 56,48</t>
+          <t>26,05; 57,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,66; 43,9</t>
+          <t>19,99; 43,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,53; 47,57</t>
+          <t>22,51; 48,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 28,72</t>
+          <t>6,01; 26,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,95</t>
+          <t>16,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,23; 22,27</t>
+          <t>13,45; 22,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 25,09</t>
+          <t>16,35; 24,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 20,67</t>
+          <t>11,83; 21,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 43,36</t>
+          <t>12,26; 21,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,47; 57,54</t>
+          <t>31,02; 57,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 52,91</t>
+          <t>31,82; 52,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,98; 44,79</t>
+          <t>22,7; 45,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 211,08</t>
+          <t>24,76; 48,82</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,07</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 24,2</t>
+          <t>13,49; 23,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,81; 25,1</t>
+          <t>14,7; 25,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 19,89</t>
+          <t>9,55; 19,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 32,05</t>
+          <t>2,09; 12,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,8; 67,42</t>
+          <t>32,14; 66,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 56,28</t>
+          <t>29,48; 56,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,42; 45,61</t>
+          <t>19,34; 45,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 63,23</t>
+          <t>3,68; 24,96</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,08</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,15; 23,23</t>
+          <t>14,3; 22,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,26; 25,23</t>
+          <t>16,07; 25,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,35</t>
+          <t>7,73; 16,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 19,02</t>
+          <t>5,95; 15,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,48; 61,13</t>
+          <t>32,73; 59,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,03; 51,23</t>
+          <t>30,21; 51,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 32,36</t>
+          <t>13,91; 33,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,99; 34,27</t>
+          <t>10,4; 29,22</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,93</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 20,45</t>
+          <t>15,47; 20,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 22,03</t>
+          <t>17,44; 22,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,31</t>
+          <t>12,6; 17,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 29,34</t>
+          <t>8,73; 13,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,4; 52,31</t>
+          <t>37,26; 52,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,5; 45,08</t>
+          <t>33,54; 44,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,34; 35,68</t>
+          <t>24,46; 35,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,5; 75,12</t>
+          <t>16,25; 26,76</t>
         </is>
       </c>
     </row>
